--- a/MainTop/25.12.2025 имена/25.12.2025 имена_объединенно_по_штрихкоду.xlsx
+++ b/MainTop/25.12.2025 имена/25.12.2025 имена_объединенно_по_штрихкоду.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\25.12.2025 имена\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE103E0F-0AA2-4254-96F3-D4654AEA9374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F778E275-0C68-4A01-9123-16D1E36E6788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
     <t>штрихкод</t>
   </si>
   <si>
-    <t>количество</t>
-  </si>
-  <si>
     <t>Термобирки Михаил</t>
   </si>
   <si>
@@ -641,6 +638,9 @@
   </si>
   <si>
     <t>OZN1302409156</t>
+  </si>
+  <si>
+    <t>Num_Copies</t>
   </si>
 </sst>
 </file>
@@ -1044,6 +1044,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1053,15 +1057,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -1069,10 +1073,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -1080,10 +1084,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1091,10 +1095,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -1102,10 +1106,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -1113,10 +1117,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -1124,10 +1128,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -1135,10 +1139,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -1146,10 +1150,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -1157,10 +1161,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -1168,10 +1172,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -1179,10 +1183,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -1190,10 +1194,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -1201,10 +1205,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -1212,10 +1216,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -1223,10 +1227,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -1234,10 +1238,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -1245,10 +1249,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -1256,10 +1260,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -1267,10 +1271,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -1278,10 +1282,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -1289,10 +1293,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -1300,10 +1304,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -1311,10 +1315,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -1322,10 +1326,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -1333,10 +1337,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -1344,10 +1348,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -1355,10 +1359,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -1366,10 +1370,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -1377,10 +1381,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -1388,10 +1392,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -1399,10 +1403,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -1410,10 +1414,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1421,10 +1425,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -1432,10 +1436,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -1443,10 +1447,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -1454,10 +1458,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -1465,10 +1469,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1476,10 +1480,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -1487,10 +1491,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -1498,10 +1502,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1509,10 +1513,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -1520,10 +1524,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -1531,10 +1535,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1542,10 +1546,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -1553,10 +1557,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -1564,10 +1568,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -1575,10 +1579,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -1586,10 +1590,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -1597,10 +1601,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -1608,10 +1612,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -1619,10 +1623,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -1630,10 +1634,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -1641,10 +1645,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -1652,10 +1656,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -1663,10 +1667,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -1674,10 +1678,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -1685,10 +1689,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -1696,10 +1700,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -1707,10 +1711,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -1718,10 +1722,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -1729,10 +1733,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -1740,10 +1744,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -1751,10 +1755,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -1762,10 +1766,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -1773,10 +1777,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -1784,10 +1788,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C68">
         <v>2</v>
@@ -1795,10 +1799,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -1806,10 +1810,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -1817,10 +1821,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -1828,10 +1832,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -1839,10 +1843,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -1850,10 +1854,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -1861,10 +1865,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -1872,10 +1876,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -1883,10 +1887,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -1894,10 +1898,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -1905,10 +1909,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -1916,10 +1920,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -1927,10 +1931,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -1938,10 +1942,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -1949,10 +1953,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -1960,10 +1964,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -1971,10 +1975,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -1982,10 +1986,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -1993,10 +1997,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -2004,10 +2008,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -2015,10 +2019,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -2026,10 +2030,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -2037,10 +2041,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -2048,10 +2052,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -2059,10 +2063,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -2070,10 +2074,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -2081,10 +2085,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -2092,10 +2096,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -2103,10 +2107,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -2114,10 +2118,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2125,10 +2129,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -2136,10 +2140,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -2147,10 +2151,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -2158,10 +2162,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -2169,10 +2173,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C103">
         <v>1</v>

--- a/MainTop/25.12.2025 имена/25.12.2025 имена_объединенно_по_штрихкоду.xlsx
+++ b/MainTop/25.12.2025 имена/25.12.2025 имена_объединенно_по_штрихкоду.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\25.12.2025 имена\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F778E275-0C68-4A01-9123-16D1E36E6788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF513BCC-BFFD-45ED-9D80-6CB7FF4CB153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
